--- a/RP7.3/output/RP7.3_calculation_log.xlsx
+++ b/RP7.3/output/RP7.3_calculation_log.xlsx
@@ -33,7 +33,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -430,21 +429,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,7 +464,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>scenario</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -525,10 +524,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D2" t="n">
+        <v>2023</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -537,7 +534,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(RI_base-RI)+(CIRC-CIRC_base)-(IEQ-IEQ_base)-(WEX-WEX_base)</t>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -551,7 +548,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8151</v>
+        <v>6283.68</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -565,7 +562,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -585,10 +582,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D3" t="n">
+        <v>2023</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -597,7 +592,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(Ex_VA-..)-(Ex_econ_in-..)-(Ex_INV-..)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -611,7 +606,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9384.1</v>
+        <v>7234.288</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -625,7 +620,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -645,10 +640,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D4" t="n">
+        <v>2023</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -657,7 +650,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(Ex_SV-..)+(Ex_train-..)-(Ex_lost-..)-(Ex_CO2-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -671,7 +664,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5831.1</v>
+        <v>4495.248</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -685,7 +678,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -705,10 +698,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D5" t="n">
+        <v>2023</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -717,7 +708,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(loss_base)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -731,7 +722,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2537.26</v>
+        <v>22.5568</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -745,7 +736,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -765,10 +756,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D6" t="n">
+        <v>2023</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -791,7 +780,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>25903.46</v>
+        <v>18035.7728</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -805,7 +794,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -825,10 +814,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D7" t="n">
+        <v>2023</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -851,7 +838,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5900.232</v>
+        <v>3788.0178</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -865,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -885,10 +872,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D8" t="n">
+        <v>2023</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -911,7 +896,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>197600</v>
+        <v>195700</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +910,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -945,10 +930,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D9" t="n">
+        <v>2023</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -971,7 +954,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.0299</v>
+        <v>0.0194</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -985,7 +968,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1005,10 +988,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D10" t="n">
+        <v>2023</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1031,7 +1012,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1045,7 +1026,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1065,10 +1046,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+      <c r="D11" t="n">
+        <v>2023</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1091,7 +1070,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0867</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1105,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1125,10 +1104,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D12" t="n">
+        <v>2024</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1137,7 +1114,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(RI_base-RI)+(CIRC-CIRC_base)-(IEQ-IEQ_base)-(WEX-WEX_base)</t>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1151,7 +1128,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>16302</v>
+        <v>10210.98</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1165,7 +1142,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1185,10 +1162,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D13" t="n">
+        <v>2024</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1197,7 +1172,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(Ex_VA-..)-(Ex_econ_in-..)-(Ex_INV-..)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1211,7 +1186,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>18768.2</v>
+        <v>11755.718</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1225,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1245,10 +1220,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D14" t="n">
+        <v>2024</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1257,7 +1230,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(Ex_SV-..)+(Ex_train-..)-(Ex_lost-..)-(Ex_CO2-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1271,7 +1244,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>11662.2</v>
+        <v>7304.778</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1285,7 +1258,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1305,10 +1278,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D15" t="n">
+        <v>2024</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1317,7 +1288,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(loss_base)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1331,7 +1302,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>15106.52</v>
+        <v>6078.6548</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1345,7 +1316,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1336,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D16" t="n">
+        <v>2024</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1391,7 +1360,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>61838.92</v>
+        <v>35350.1308</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1405,7 +1374,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1425,10 +1394,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D17" t="n">
+        <v>2024</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1451,7 +1418,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>15746.583</v>
+        <v>8532.1687</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1465,7 +1432,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1485,10 +1452,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D18" t="n">
+        <v>2024</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1511,7 +1476,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>186200</v>
+        <v>190000</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1525,7 +1490,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1545,10 +1510,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D19" t="n">
+        <v>2024</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1571,7 +1534,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0449</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1585,7 +1548,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1605,10 +1568,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D20" t="n">
+        <v>2024</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1631,7 +1592,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.163</v>
+        <v>0.159</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1645,7 +1606,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1665,10 +1626,8 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D21" t="n">
+        <v>2024</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1691,7 +1650,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.1238</v>
+        <v>0.102</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1705,7 +1664,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1676,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1725,37 +1684,35 @@
           <t>D020</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D22" t="n">
+        <v>2025</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TSI_rel</t>
+          <t>f_env</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TSI_abs_rt/TSI_abs_hist</t>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>module_terms.csv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>coefficients_master.xlsx</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3919</v>
+        <v>14138.28</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>adim</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1765,7 +1722,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1782,22 +1739,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2025</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>f_env</t>
+          <t>f_econ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(RI_base-RI)+(CIRC-CIRC_base)-(IEQ-IEQ_base)-(WEX-WEX_base)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1811,7 +1766,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13228.8</v>
+        <v>16277.148</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1825,7 +1780,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1842,22 +1797,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2025</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>f_econ</t>
+          <t>f_soc</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(Ex_VA-..)-(Ex_econ_in-..)-(Ex_INV-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1871,7 +1824,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>15230.08</v>
+        <v>10114.308</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1885,7 +1838,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1902,22 +1855,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2025</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>f_soc</t>
+          <t>f_tech</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(Ex_SV-..)+(Ex_train-..)-(Ex_lost-..)-(Ex_CO2-..)</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1931,7 +1882,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>9463.68</v>
+        <v>12134.7528</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1945,7 +1896,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -1962,36 +1913,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2025</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>f_tech</t>
+          <t>SA_raw</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(loss_base)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>sum(f_i)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>module_terms.csv</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>coefficients_master.xlsx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4117.888</v>
+        <v>52664.4888</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2005,7 +1954,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2017,27 +1966,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2025</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SA_raw</t>
+          <t>SA_w</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>sum(f_i)</t>
+          <t>sum(w_i*f_i)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2047,11 +1994,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ahp_weights.xlsx</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>42040.448</v>
+        <v>13276.3196</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2065,7 +2012,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2077,41 +2024,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2025</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SA_w</t>
+          <t>Ex_ref</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>sum(w_i*f_i)</t>
+          <t>Ex_el+Ex_fuel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>energy_exergy.csv</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ahp_weights.xlsx</t>
+          <t>EL_EX,GAS_EX</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9575.8789</v>
+        <v>184300</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2125,7 +2070,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2137,45 +2082,43 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2025</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ex_ref</t>
+          <t>Phi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ex_el+Ex_fuel</t>
+          <t>SA_w/Ex_ref</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>energy_exergy.csv</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>EL_EX,GAS_EX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>316800</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>GJ</t>
+          <t>adim</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2185,7 +2128,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2197,32 +2140,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2025</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Phi</t>
+          <t>Psi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SA_w/Ex_ref</t>
+          <t>Ex_useful/Ex_ref</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>energy_exergy.csv</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2231,7 +2172,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.0302</v>
+        <v>0.164</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2245,7 +2186,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2257,32 +2198,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2025</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Psi</t>
+          <t>TSI_abs</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ex_useful/Ex_ref</t>
+          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>energy_exergy.csv</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2291,7 +2230,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.156</v>
+        <v>0.118</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2305,7 +2244,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2322,27 +2261,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>D060</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2025</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TSI_abs</t>
+          <t>TSI_rel</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
+          <t>TSI(2025)/TSI(2023)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2351,7 +2288,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.0931</v>
+        <v>1.3616</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2365,7 +2302,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2385,10 +2322,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D33" t="n">
+        <v>2023</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2397,7 +2332,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(RI_base-RI)+(CIRC-CIRC_base)-(IEQ-IEQ_base)-(WEX-WEX_base)</t>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2411,7 +2346,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>26457.6</v>
+        <v>10083.84</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2425,7 +2360,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2445,10 +2380,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D34" t="n">
+        <v>2023</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2457,7 +2390,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>(Ex_VA-..)-(Ex_econ_in-..)-(Ex_INV-..)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2471,7 +2404,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>30460.16</v>
+        <v>11609.344</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2485,7 +2418,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2505,10 +2438,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D35" t="n">
+        <v>2023</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2517,7 +2448,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>(Ex_SV-..)+(Ex_train-..)-(Ex_lost-..)-(Ex_CO2-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2531,7 +2462,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>18927.36</v>
+        <v>7213.824</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2545,7 +2476,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2565,10 +2496,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D36" t="n">
+        <v>2023</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2577,7 +2506,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>(loss_base)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2591,7 +2520,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>24517.376</v>
+        <v>36.1984</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2605,7 +2534,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2625,10 +2554,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D37" t="n">
+        <v>2023</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2651,7 +2578,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>100362.496</v>
+        <v>28943.2064</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2665,7 +2592,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2685,10 +2612,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D38" t="n">
+        <v>2023</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2711,7 +2636,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>25556.1767</v>
+        <v>6078.8845</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2725,7 +2650,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2745,10 +2670,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D39" t="n">
+        <v>2023</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2771,7 +2694,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>295680</v>
+        <v>313600</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2785,7 +2708,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2805,10 +2728,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D40" t="n">
+        <v>2023</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2831,7 +2752,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.0864</v>
+        <v>0.0194</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2845,7 +2766,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2865,10 +2786,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D41" t="n">
+        <v>2023</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2891,7 +2810,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.172</v>
+        <v>0.163</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2905,7 +2824,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2925,10 +2844,8 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D42" t="n">
+        <v>2023</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2951,7 +2868,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.1292</v>
+        <v>0.0912</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2965,7 +2882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2894,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2985,37 +2902,35 @@
           <t>D060</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+      <c r="D43" t="n">
+        <v>2024</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TSI_rel</t>
+          <t>f_env</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TSI_abs_rt/TSI_abs_hist</t>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>module_terms.csv</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>coefficients_master.xlsx</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3877</v>
+        <v>16386.24</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>adim</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3025,7 +2940,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3042,22 +2957,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2024</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>f_env</t>
+          <t>f_econ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>(RI_base-RI)+(CIRC-CIRC_base)-(IEQ-IEQ_base)-(WEX-WEX_base)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3071,7 +2984,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10342.8</v>
+        <v>18865.184</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3085,7 +2998,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3102,22 +3015,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2024</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>f_econ</t>
+          <t>f_soc</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>(Ex_VA-..)-(Ex_econ_in-..)-(Ex_INV-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3131,7 +3042,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>11907.48</v>
+        <v>11722.464</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3145,7 +3056,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3162,22 +3073,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2024</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>f_soc</t>
+          <t>f_tech</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>(Ex_SV-..)+(Ex_train-..)-(Ex_lost-..)-(Ex_CO2-..)</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3191,7 +3100,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7399.08</v>
+        <v>9754.822399999999</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3205,7 +3114,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3222,36 +3131,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2024</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>f_tech</t>
+          <t>SA_raw</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>(loss_base)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>sum(f_i)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>module_terms.csv</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>coefficients_master.xlsx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3219.528</v>
+        <v>56728.7104</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3265,7 +3172,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3277,27 +3184,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2024</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SA_raw</t>
+          <t>SA_w</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>sum(f_i)</t>
+          <t>sum(w_i*f_i)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3307,11 +3212,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ahp_weights.xlsx</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>32868.888</v>
+        <v>13692.1396</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3325,7 +3230,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3337,41 +3242,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2024</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SA_w</t>
+          <t>Ex_ref</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>sum(w_i*f_i)</t>
+          <t>Ex_el+Ex_fuel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>energy_exergy.csv</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ahp_weights.xlsx</t>
+          <t>EL_EX,GAS_EX</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7486.8016</v>
+        <v>304000</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3385,7 +3288,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3397,45 +3300,43 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2024</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ex_ref</t>
+          <t>Phi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ex_el+Ex_fuel</t>
+          <t>SA_w/Ex_ref</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>energy_exergy.csv</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>EL_EX,GAS_EX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>243780</v>
+        <v>0.045</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>GJ</t>
+          <t>adim</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3445,7 +3346,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3457,32 +3358,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2024</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Phi</t>
+          <t>Psi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SA_w/Ex_ref</t>
+          <t>Ex_useful/Ex_ref</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>energy_exergy.csv</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3491,7 +3390,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.0307</v>
+        <v>0.168</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3505,7 +3404,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3517,32 +3416,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2024</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Psi</t>
+          <t>TSI_abs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ex_useful/Ex_ref</t>
+          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>energy_exergy.csv</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3551,7 +3448,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.161</v>
+        <v>0.1065</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3565,7 +3462,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3577,45 +3474,43 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2025</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TSI_abs</t>
+          <t>f_env</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>module_terms.csv</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>coefficients_master.xlsx</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.0959</v>
+        <v>22688.64</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>adim</t>
+          <t>GJ</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3625,7 +3520,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3642,22 +3537,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2025</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>f_env</t>
+          <t>f_econ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>(RI_base-RI)+(CIRC-CIRC_base)-(IEQ-IEQ_base)-(WEX-WEX_base)</t>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3671,7 +3564,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>20685.6</v>
+        <v>26121.024</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3685,7 +3578,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3702,22 +3595,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2025</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>f_econ</t>
+          <t>f_soc</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>(Ex_VA-..)-(Ex_econ_in-..)-(Ex_INV-..)</t>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3731,7 +3622,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>23814.96</v>
+        <v>16231.104</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3745,7 +3636,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3762,22 +3653,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2025</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>f_soc</t>
+          <t>f_tech</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>(Ex_SV-..)+(Ex_train-..)-(Ex_lost-..)-(Ex_CO2-..)</t>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3791,7 +3680,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>14798.16</v>
+        <v>19473.4464</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3805,7 +3694,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3822,36 +3711,34 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2025</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>f_tech</t>
+          <t>SA_raw</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>(loss_base)-(loss)-inv-qual_MTS-qual_MTO</t>
+          <t>sum(f_i)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>module_terms.csv</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>coefficients_master.xlsx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>19168.656</v>
+        <v>84514.2144</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3865,7 +3752,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3877,27 +3764,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2025</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SA_raw</t>
+          <t>SA_w</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>sum(f_i)</t>
+          <t>sum(w_i*f_i)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3907,11 +3792,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ahp_weights.xlsx</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>78467.376</v>
+        <v>21305.3947</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3925,7 +3810,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3937,41 +3822,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2025</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SA_w</t>
+          <t>Ex_ref</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>sum(w_i*f_i)</t>
+          <t>Ex_el+Ex_fuel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>energy_exergy.csv</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ahp_weights.xlsx</t>
+          <t>EL_EX,GAS_EX</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>19980.8316</v>
+        <v>294400</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3985,7 +3868,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -3997,45 +3880,43 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2025</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ex_ref</t>
+          <t>Phi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ex_el+Ex_fuel</t>
+          <t>SA_w/Ex_ref</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>energy_exergy.csv</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>EL_EX,GAS_EX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>231030</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>GJ</t>
+          <t>adim</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4045,7 +3926,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -4057,32 +3938,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2025</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Phi</t>
+          <t>Psi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SA_w/Ex_ref</t>
+          <t>Ex_useful/Ex_ref</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>energy_exergy.csv</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4091,7 +3970,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4105,7 +3984,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -4117,32 +3996,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2025</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Psi</t>
+          <t>TSI_abs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ex_useful/Ex_ref</t>
+          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>energy_exergy.csv</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4151,7 +4028,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.175</v>
+        <v>0.1227</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4165,7 +4042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -4182,27 +4059,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>D240</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
+          <t>D060</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2025</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TSI_abs</t>
+          <t>TSI_rel</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
+          <t>TSI(2025)/TSI(2023)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4211,7 +4086,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.1307</v>
+        <v>1.3453</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4225,7 +4100,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>beta-1.0-DEMO</t>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -4237,55 +4112,1793 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>f_env</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>7796.88</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>R064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>f_econ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>8976.407999999999</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>R065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>f_soc</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>5577.768</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>R066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>f_tech</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>27.9888</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>R067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SA_raw</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>sum(f_i)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>22379.0448</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>R068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SA_w</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>sum(w_i*f_i)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ahp_weights.xlsx</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>4700.2266</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>R069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Ex_ref</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ex_el+Ex_fuel</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>energy_exergy.csv</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>EL_EX,GAS_EX</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>242250</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>R070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Phi</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SA_w/Ex_ref</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>R071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Psi</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ex_useful/Ex_ref</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>energy_exergy.csv</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>R072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>D240</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>realtime</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="D73" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>TSI_abs</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>R073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>f_env</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>12669.93</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>R074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>f_econ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>14586.663</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>R075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>f_soc</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>9063.873</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>R076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>f_tech</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>7542.4818</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>R077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SA_raw</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>sum(f_i)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>43862.9478</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>R078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SA_w</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>sum(w_i*f_i)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ahp_weights.xlsx</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>10586.8369</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>R079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ex_ref</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ex_el+Ex_fuel</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>energy_exergy.csv</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>EL_EX,GAS_EX</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>235620</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>R080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Phi</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SA_w/Ex_ref</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>R081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Psi</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ex_useful/Ex_ref</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>energy_exergy.csv</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>R082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>TSI_abs</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>R083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>f_env</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>(RI_ref-RI)+(CIRC-CIRC_ref)-(IEQ-IEQ_ref)-(WEX-WEX_ref)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>17542.98</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>R084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>f_econ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>(VA-VA_ref)-(econ_in-..)-(INV-..)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>20196.918</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>R085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>f_soc</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>(SV-..)+(train-..)-(lost-..)-(CO2-..)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>12549.978</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>R086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>f_tech</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>(loss_ref)-(loss)-inv-qual_MTS-qual_MTO</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>module_terms.csv</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>coefficients_master.xlsx</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>15056.9748</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>R087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>SA_raw</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>sum(f_i)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>65346.8508</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>R088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SA_w</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>sum(w_i*f_i)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ahp_weights.xlsx</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>16473.4472</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>R089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ex_ref</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ex_el+Ex_fuel</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>energy_exergy.csv</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>EL_EX,GAS_EX</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>229500</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>R090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Phi</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SA_w/Ex_ref</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>R091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Psi</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ex_useful/Ex_ref</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>energy_exergy.csv</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>R092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>TSI_abs</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>alpha*Phi+beta*Psi (a=b=0.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>adim</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>R093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>TSI_rel</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>TSI_abs_rt/TSI_abs_hist</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TSI(2025)/TSI(2023)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="I94" t="n">
+        <v>1.3222</v>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>adim</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>beta-1.0-DEMO</t>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>beta-1.1</t>
         </is>
       </c>
     </row>
@@ -4402,7 +6015,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Valori DIMOSTRATIVI / NON VALIDATI (confidence C). Da rigenerare su dati primari.</t>
+          <t>Serie 2023-2025 provvisorie, in corso di consolidamento. Struttura di calcolo invariata al consolidamento.</t>
         </is>
       </c>
     </row>
